--- a/full/sliding_window_results_window_2.xlsx
+++ b/full/sliding_window_results_window_2.xlsx
@@ -463,13 +463,13 @@
         <v>29.15</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>29.02381252314289</v>
       </c>
       <c r="D2" t="n">
-        <v>-29.15</v>
+        <v>-0.1261874768571047</v>
       </c>
       <c r="E2" t="n">
-        <v>849.7225</v>
+        <v>0.01592327931556235</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.35</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>28.75368709650346</v>
       </c>
       <c r="D3" t="n">
-        <v>-29.35</v>
+        <v>-0.5963129034965462</v>
       </c>
       <c r="E3" t="n">
-        <v>861.4225000000001</v>
+        <v>0.3555890788764812</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.37</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>28.83047841649158</v>
       </c>
       <c r="D4" t="n">
-        <v>-29.37</v>
+        <v>-0.5395215835084208</v>
       </c>
       <c r="E4" t="n">
-        <v>862.5969</v>
+        <v>0.2910835390714339</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.54</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>29.05125791563309</v>
       </c>
       <c r="D5" t="n">
-        <v>-29.54</v>
+        <v>-0.4887420843669119</v>
       </c>
       <c r="E5" t="n">
-        <v>872.6116</v>
+        <v>0.2388688250313137</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.55</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>29.5158752386351</v>
       </c>
       <c r="D6" t="n">
-        <v>-29.55</v>
+        <v>-0.03412476136489673</v>
       </c>
       <c r="E6" t="n">
-        <v>873.2025</v>
+        <v>0.001164499338211148</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.75</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>29.74304293528138</v>
       </c>
       <c r="D7" t="n">
-        <v>-29.75</v>
+        <v>-0.006957064718619677</v>
       </c>
       <c r="E7" t="n">
-        <v>885.0625</v>
+        <v>4.840074949906268e-05</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.84</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>29.58077201361602</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.84</v>
+        <v>-0.2592279863839799</v>
       </c>
       <c r="E8" t="n">
-        <v>890.4256</v>
+        <v>0.06719914892469288</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.81</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>29.68211377194293</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.81</v>
+        <v>-0.1278862280570685</v>
       </c>
       <c r="E9" t="n">
-        <v>888.6360999999999</v>
+        <v>0.01635488732666454</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.92</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>29.54752795107213</v>
       </c>
       <c r="D10" t="n">
-        <v>-29.92</v>
+        <v>-0.3724720489278681</v>
       </c>
       <c r="E10" t="n">
-        <v>895.2064000000001</v>
+        <v>0.1387354272325242</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.98</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>29.75683841497857</v>
       </c>
       <c r="D11" t="n">
-        <v>-29.98</v>
+        <v>-0.2231615850214261</v>
       </c>
       <c r="E11" t="n">
-        <v>898.8004000000001</v>
+        <v>0.0498010930292752</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.04</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>29.73810743862573</v>
       </c>
       <c r="D12" t="n">
-        <v>-30.04</v>
+        <v>-0.3018925613742667</v>
       </c>
       <c r="E12" t="n">
-        <v>902.4015999999999</v>
+        <v>0.09113911861311537</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.21</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>29.76147510426867</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.21</v>
+        <v>-0.4485248957313317</v>
       </c>
       <c r="E13" t="n">
-        <v>912.6441000000001</v>
+        <v>0.201174582090802</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.22</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>29.9606812511153</v>
       </c>
       <c r="D14" t="n">
-        <v>-30.22</v>
+        <v>-0.2593187488846951</v>
       </c>
       <c r="E14" t="n">
-        <v>913.2483999999999</v>
+        <v>0.06724621352312354</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.38</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>29.87607033507794</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.38</v>
+        <v>-0.5039296649220582</v>
       </c>
       <c r="E15" t="n">
-        <v>922.9444</v>
+        <v>0.2539451071884578</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.44</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29.93461129704251</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.44</v>
+        <v>-0.5053887029574931</v>
       </c>
       <c r="E16" t="n">
-        <v>926.5936</v>
+        <v>0.2554177410770572</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.48</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>30.32728585566579</v>
       </c>
       <c r="D17" t="n">
-        <v>-30.48</v>
+        <v>-0.1527141443342082</v>
       </c>
       <c r="E17" t="n">
-        <v>929.0304</v>
+        <v>0.02332160987972936</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.69</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>30.28804325780069</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.69</v>
+        <v>-0.4019567421993067</v>
       </c>
       <c r="E18" t="n">
-        <v>941.8761000000001</v>
+        <v>0.1615692225994799</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.75</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31.35097886077029</v>
       </c>
       <c r="D19" t="n">
-        <v>-30.75</v>
+        <v>0.6009788607702902</v>
       </c>
       <c r="E19" t="n">
-        <v>945.5625</v>
+        <v>0.3611755910927558</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.94</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>31.49617511377952</v>
       </c>
       <c r="D20" t="n">
-        <v>-30.94</v>
+        <v>0.5561751137795206</v>
       </c>
       <c r="E20" t="n">
-        <v>957.2836000000001</v>
+        <v>0.3093307571876626</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.95</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>31.79926696385362</v>
       </c>
       <c r="D21" t="n">
-        <v>-30.95</v>
+        <v>0.8492669638536192</v>
       </c>
       <c r="E21" t="n">
-        <v>957.9024999999999</v>
+        <v>0.7212543758931446</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.02</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>31.36317758864411</v>
       </c>
       <c r="D22" t="n">
-        <v>-31.02</v>
+        <v>0.3431775886441137</v>
       </c>
       <c r="E22" t="n">
-        <v>962.2404</v>
+        <v>0.1177708573475885</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.12</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>31.1702265847368</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.12</v>
+        <v>0.05022658473680153</v>
       </c>
       <c r="E23" t="n">
-        <v>968.4544000000001</v>
+        <v>0.002522709814323104</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.28</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>31.46856948383135</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.28</v>
+        <v>0.1885694838313441</v>
       </c>
       <c r="E24" t="n">
-        <v>978.4384000000001</v>
+        <v>0.03555845023241954</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.38</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>31.44570478500628</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.38</v>
+        <v>0.06570478500628596</v>
       </c>
       <c r="E25" t="n">
-        <v>984.7044</v>
+        <v>0.00431711877272226</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.58</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>31.15478729408748</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.58</v>
+        <v>-0.4252127059125144</v>
       </c>
       <c r="E26" t="n">
-        <v>997.2963999999999</v>
+        <v>0.1808058452694424</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.65</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>31.58687360071157</v>
       </c>
       <c r="D27" t="n">
-        <v>-31.65</v>
+        <v>-0.06312639928842856</v>
       </c>
       <c r="E27" t="n">
-        <v>1001.7225</v>
+        <v>0.003984942287122113</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.88</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>31.54552549821508</v>
       </c>
       <c r="D28" t="n">
-        <v>-31.88</v>
+        <v>-0.3344745017849213</v>
       </c>
       <c r="E28" t="n">
-        <v>1016.3344</v>
+        <v>0.1118731923442713</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.28</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>31.93445834616257</v>
       </c>
       <c r="D29" t="n">
-        <v>-32.28</v>
+        <v>-0.3455416538374294</v>
       </c>
       <c r="E29" t="n">
-        <v>1041.9984</v>
+        <v>0.1193990345367059</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.45</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>32.3731268104054</v>
       </c>
       <c r="D30" t="n">
-        <v>-32.45</v>
+        <v>-0.07687318959460754</v>
       </c>
       <c r="E30" t="n">
-        <v>1053.0025</v>
+        <v>0.005909487278448477</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.85</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>33.32158228747896</v>
       </c>
       <c r="D31" t="n">
-        <v>-32.85</v>
+        <v>0.4715822874789595</v>
       </c>
       <c r="E31" t="n">
-        <v>1079.1225</v>
+        <v>0.222389853863888</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.9</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>33.54253931907255</v>
       </c>
       <c r="D32" t="n">
-        <v>-32.9</v>
+        <v>0.6425393190725472</v>
       </c>
       <c r="E32" t="n">
-        <v>1082.41</v>
+        <v>0.4128567765542127</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>34.09321692438535</v>
       </c>
       <c r="D33" t="n">
-        <v>-33.1</v>
+        <v>0.9932169243853508</v>
       </c>
       <c r="E33" t="n">
-        <v>1095.61</v>
+        <v>0.9864798588854957</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.4</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>33.39833273060193</v>
       </c>
       <c r="D34" t="n">
-        <v>-33.4</v>
+        <v>-0.001667269398069493</v>
       </c>
       <c r="E34" t="n">
-        <v>1115.56</v>
+        <v>2.77978724573901e-06</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.7</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>34.39789626642995</v>
       </c>
       <c r="D35" t="n">
-        <v>-33.7</v>
+        <v>0.6978962664299502</v>
       </c>
       <c r="E35" t="n">
-        <v>1135.69</v>
+        <v>0.487059198696864</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.1</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>35.00093290383575</v>
       </c>
       <c r="D36" t="n">
-        <v>-34.1</v>
+        <v>0.900932903835745</v>
       </c>
       <c r="E36" t="n">
-        <v>1162.81</v>
+        <v>0.8116800972139077</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.4</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>35.30233051941863</v>
       </c>
       <c r="D37" t="n">
-        <v>-34.4</v>
+        <v>0.9023305194186335</v>
       </c>
       <c r="E37" t="n">
-        <v>1183.36</v>
+        <v>0.8142003662743009</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.9</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>34.95301991141709</v>
       </c>
       <c r="D38" t="n">
-        <v>-34.9</v>
+        <v>0.05301991141708839</v>
       </c>
       <c r="E38" t="n">
-        <v>1218.01</v>
+        <v>0.0028111110066759</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.3</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>34.72306620000119</v>
       </c>
       <c r="D39" t="n">
-        <v>-35.3</v>
+        <v>-0.5769337999988053</v>
       </c>
       <c r="E39" t="n">
-        <v>1246.09</v>
+        <v>0.3328526095810615</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.7</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>35.16858681465516</v>
       </c>
       <c r="D40" t="n">
-        <v>-35.7</v>
+        <v>-0.5314131853448387</v>
       </c>
       <c r="E40" t="n">
-        <v>1274.49</v>
+        <v>0.2823999735583479</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.3</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>35.61014068077346</v>
       </c>
       <c r="D41" t="n">
-        <v>-36.3</v>
+        <v>-0.6898593192265352</v>
       </c>
       <c r="E41" t="n">
-        <v>1317.69</v>
+        <v>0.4759058803236986</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.8</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>35.68210540268343</v>
       </c>
       <c r="D42" t="n">
-        <v>-36.8</v>
+        <v>-1.117894597316571</v>
       </c>
       <c r="E42" t="n">
-        <v>1354.24</v>
+        <v>1.249688330709579</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.3</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>36.89876293834338</v>
       </c>
       <c r="D43" t="n">
-        <v>-37.3</v>
+        <v>-0.4012370616566159</v>
       </c>
       <c r="E43" t="n">
-        <v>1391.29</v>
+        <v>0.160991179646835</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>37.87543651653033</v>
       </c>
       <c r="D44" t="n">
-        <v>-37.9</v>
+        <v>-0.02456348346967019</v>
       </c>
       <c r="E44" t="n">
-        <v>1436.41</v>
+        <v>0.0006033647201647606</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.5</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>38.58766495887683</v>
       </c>
       <c r="D45" t="n">
-        <v>-38.5</v>
+        <v>0.08766495887682879</v>
       </c>
       <c r="E45" t="n">
-        <v>1482.25</v>
+        <v>0.007685145014876083</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.9</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>39.10540492532465</v>
       </c>
       <c r="D46" t="n">
-        <v>-38.9</v>
+        <v>0.2054049253246504</v>
       </c>
       <c r="E46" t="n">
-        <v>1513.21</v>
+        <v>0.0421911833476252</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.4</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>40.05100399181302</v>
       </c>
       <c r="D47" t="n">
-        <v>-39.4</v>
+        <v>0.6510039918130204</v>
       </c>
       <c r="E47" t="n">
-        <v>1552.36</v>
+        <v>0.4238061973564871</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.9</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>40.56251715606416</v>
       </c>
       <c r="D48" t="n">
-        <v>-39.9</v>
+        <v>0.6625171560641618</v>
       </c>
       <c r="E48" t="n">
-        <v>1592.01</v>
+        <v>0.438928982079345</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.1</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>38.33997861283432</v>
       </c>
       <c r="D49" t="n">
-        <v>-40.1</v>
+        <v>-1.760021387165686</v>
       </c>
       <c r="E49" t="n">
-        <v>1608.01</v>
+        <v>3.097675283280626</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.6</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>40.43296999164407</v>
       </c>
       <c r="D50" t="n">
-        <v>-40.6</v>
+        <v>-0.1670300083559297</v>
       </c>
       <c r="E50" t="n">
-        <v>1648.36</v>
+        <v>0.02789902369138196</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.9</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>40.02033061713695</v>
       </c>
       <c r="D51" t="n">
-        <v>-40.9</v>
+        <v>-0.8796693828630495</v>
       </c>
       <c r="E51" t="n">
-        <v>1672.81</v>
+        <v>0.7738182231466584</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-1652.95</v>
+        <v>-3.821628583580964</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>55253.15850000001</v>
+        <v>15.25440955466331</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1105.06317</v>
+        <v>0.3050881910932662</v>
       </c>
     </row>
   </sheetData>

--- a/full/sliding_window_results_window_2.xlsx
+++ b/full/sliding_window_results_window_2.xlsx
@@ -463,13 +463,13 @@
         <v>29.15</v>
       </c>
       <c r="C2" t="n">
-        <v>29.02381252314289</v>
+        <v>28.75736457323343</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1261874768571047</v>
+        <v>-0.3926354267665708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01592327931556235</v>
+        <v>0.1541625783521672</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.35</v>
       </c>
       <c r="C3" t="n">
-        <v>28.75368709650346</v>
+        <v>28.89012936936095</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5963129034965462</v>
+        <v>-0.459870630639049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3555890788764812</v>
+        <v>0.2114809969243566</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.37</v>
       </c>
       <c r="C4" t="n">
-        <v>28.83047841649158</v>
+        <v>29.00263317446207</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5395215835084208</v>
+        <v>-0.3673668255379283</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2910835390714339</v>
+        <v>0.1349583845058147</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.54</v>
       </c>
       <c r="C5" t="n">
-        <v>29.05125791563309</v>
+        <v>29.58799906097413</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4887420843669119</v>
+        <v>0.04799906097413498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2388688250313137</v>
+        <v>0.002303909854398727</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.55</v>
       </c>
       <c r="C6" t="n">
-        <v>29.5158752386351</v>
+        <v>29.5720525883031</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03412476136489673</v>
+        <v>0.02205258830310086</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001164499338211148</v>
+        <v>0.000486316650866061</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.75</v>
       </c>
       <c r="C7" t="n">
-        <v>29.74304293528138</v>
+        <v>29.66959996930985</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.006957064718619677</v>
+        <v>-0.08040003069015356</v>
       </c>
       <c r="E7" t="n">
-        <v>4.840074949906268e-05</v>
+        <v>0.006464164934977634</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.84</v>
       </c>
       <c r="C8" t="n">
-        <v>29.58077201361602</v>
+        <v>29.76770804861497</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2592279863839799</v>
+        <v>-0.07229195138503286</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06719914892469288</v>
+        <v>0.005226126235055954</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>29.81</v>
       </c>
       <c r="C9" t="n">
-        <v>29.68211377194293</v>
+        <v>29.86497854201153</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1278862280570685</v>
+        <v>0.05497854201152919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01635488732666454</v>
+        <v>0.00302264008171348</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>29.92</v>
       </c>
       <c r="C10" t="n">
-        <v>29.54752795107213</v>
+        <v>30.04991131334204</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3724720489278681</v>
+        <v>0.1299113133420349</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1387354272325242</v>
+        <v>0.01687694933425237</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>29.98</v>
       </c>
       <c r="C11" t="n">
-        <v>29.75683841497857</v>
+        <v>29.98133285213877</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2231615850214261</v>
+        <v>0.00133285213876988</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0498010930292752</v>
+        <v>1.776494823823443e-06</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.04</v>
       </c>
       <c r="C12" t="n">
-        <v>29.73810743862573</v>
+        <v>29.97573598599032</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3018925613742667</v>
+        <v>-0.06426401400967663</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09113911861311537</v>
+        <v>0.004129863496635914</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.21</v>
       </c>
       <c r="C13" t="n">
-        <v>29.76147510426867</v>
+        <v>29.83390207064875</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4485248957313317</v>
+        <v>-0.3760979293512534</v>
       </c>
       <c r="E13" t="n">
-        <v>0.201174582090802</v>
+        <v>0.1414496524623004</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.22</v>
       </c>
       <c r="C14" t="n">
-        <v>29.9606812511153</v>
+        <v>29.83873899817373</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2593187488846951</v>
+        <v>-0.3812610018262639</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06724621352312354</v>
+        <v>0.1453599515135664</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.38</v>
       </c>
       <c r="C15" t="n">
-        <v>29.87607033507794</v>
+        <v>29.89660928163999</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5039296649220582</v>
+        <v>-0.4833907183600061</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2539451071884578</v>
+        <v>0.2336665865966028</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.44</v>
       </c>
       <c r="C16" t="n">
-        <v>29.93461129704251</v>
+        <v>29.96753003720536</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5053887029574931</v>
+        <v>-0.4724699627946407</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2554177410770572</v>
+        <v>0.2232278657431692</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.48</v>
       </c>
       <c r="C17" t="n">
-        <v>30.32728585566579</v>
+        <v>30.28242311564317</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1527141443342082</v>
+        <v>-0.1975768843568346</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02332160987972936</v>
+        <v>0.039036625232154</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.69</v>
       </c>
       <c r="C18" t="n">
-        <v>30.28804325780069</v>
+        <v>30.59882251499049</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4019567421993067</v>
+        <v>-0.0911774850095135</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1615692225994799</v>
+        <v>0.00831333377266006</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>30.75</v>
       </c>
       <c r="C19" t="n">
-        <v>31.35097886077029</v>
+        <v>30.2149008571282</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6009788607702902</v>
+        <v>-0.5350991428717968</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3611755910927558</v>
+        <v>0.2863310927021316</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>30.94</v>
       </c>
       <c r="C20" t="n">
-        <v>31.49617511377952</v>
+        <v>30.84043605091948</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5561751137795206</v>
+        <v>-0.09956394908051891</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3093307571876626</v>
+        <v>0.009912979956508161</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>30.95</v>
       </c>
       <c r="C21" t="n">
-        <v>31.79926696385362</v>
+        <v>30.84521530183608</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8492669638536192</v>
+        <v>-0.1047846981639218</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7212543758931446</v>
+        <v>0.01097983296930419</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.02</v>
       </c>
       <c r="C22" t="n">
-        <v>31.36317758864411</v>
+        <v>30.99114688895842</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3431775886441137</v>
+        <v>-0.02885311104157751</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1177708573475885</v>
+        <v>0.0008325020167776018</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.12</v>
       </c>
       <c r="C23" t="n">
-        <v>31.1702265847368</v>
+        <v>31.18555906041184</v>
       </c>
       <c r="D23" t="n">
-        <v>0.05022658473680153</v>
+        <v>0.06555906041184301</v>
       </c>
       <c r="E23" t="n">
-        <v>0.002522709814323104</v>
+        <v>0.004297990402083681</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.28</v>
       </c>
       <c r="C24" t="n">
-        <v>31.46856948383135</v>
+        <v>31.44428039373525</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1885694838313441</v>
+        <v>0.1642803937352504</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03555845023241954</v>
+        <v>0.02698804776580889</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.38</v>
       </c>
       <c r="C25" t="n">
-        <v>31.44570478500628</v>
+        <v>31.63073312013432</v>
       </c>
       <c r="D25" t="n">
-        <v>0.06570478500628596</v>
+        <v>0.2507331201343206</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00431711877272226</v>
+        <v>0.06286709753229164</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>31.58</v>
       </c>
       <c r="C26" t="n">
-        <v>31.15478729408748</v>
+        <v>31.80585872732023</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4252127059125144</v>
+        <v>0.2258587273202366</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1808058452694424</v>
+        <v>0.05101216470671699</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>31.65</v>
       </c>
       <c r="C27" t="n">
-        <v>31.58687360071157</v>
+        <v>31.53741977669694</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.06312639928842856</v>
+        <v>-0.1125802233030555</v>
       </c>
       <c r="E27" t="n">
-        <v>0.003984942287122113</v>
+        <v>0.01267430667896584</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>31.88</v>
       </c>
       <c r="C28" t="n">
-        <v>31.54552549821508</v>
+        <v>31.7068613435658</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3344745017849213</v>
+        <v>-0.173138656434201</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1118731923442713</v>
+        <v>0.0299769943518403</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.28</v>
       </c>
       <c r="C29" t="n">
-        <v>31.93445834616257</v>
+        <v>31.98677751000375</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3455416538374294</v>
+        <v>-0.2932224899962463</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1193990345367059</v>
+        <v>0.08597942863959879</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>32.45</v>
       </c>
       <c r="C30" t="n">
-        <v>32.3731268104054</v>
+        <v>32.02663802373436</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.07687318959460754</v>
+        <v>-0.4233619762656389</v>
       </c>
       <c r="E30" t="n">
-        <v>0.005909487278448477</v>
+        <v>0.1792353629475474</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>32.85</v>
       </c>
       <c r="C31" t="n">
-        <v>33.32158228747896</v>
+        <v>33.09891730852088</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4715822874789595</v>
+        <v>0.2489173085208805</v>
       </c>
       <c r="E31" t="n">
-        <v>0.222389853863888</v>
+        <v>0.06195982648127919</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>32.9</v>
       </c>
       <c r="C32" t="n">
-        <v>33.54253931907255</v>
+        <v>32.76343213579358</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6425393190725472</v>
+        <v>-0.1365678642064196</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4128567765542127</v>
+        <v>0.01865078153390308</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>33.1</v>
       </c>
       <c r="C33" t="n">
-        <v>34.09321692438535</v>
+        <v>33.18154110034278</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9932169243853508</v>
+        <v>0.08154110034277551</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9864798588854957</v>
+        <v>0.006648951045110584</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>33.4</v>
       </c>
       <c r="C34" t="n">
-        <v>33.39833273060193</v>
+        <v>33.14662570020763</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.001667269398069493</v>
+        <v>-0.2533742997923696</v>
       </c>
       <c r="E34" t="n">
-        <v>2.77978724573901e-06</v>
+        <v>0.06419853579527358</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>33.7</v>
       </c>
       <c r="C35" t="n">
-        <v>34.39789626642995</v>
+        <v>33.73936092168843</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6978962664299502</v>
+        <v>0.0393609216884272</v>
       </c>
       <c r="E35" t="n">
-        <v>0.487059198696864</v>
+        <v>0.001549282156162498</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>34.1</v>
       </c>
       <c r="C36" t="n">
-        <v>35.00093290383575</v>
+        <v>34.44829949989106</v>
       </c>
       <c r="D36" t="n">
-        <v>0.900932903835745</v>
+        <v>0.3482994998910627</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8116800972139077</v>
+        <v>0.1213125416243644</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>34.4</v>
       </c>
       <c r="C37" t="n">
-        <v>35.30233051941863</v>
+        <v>34.49494191103942</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9023305194186335</v>
+        <v>0.09494191103942029</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8142003662743009</v>
+        <v>0.009013966471817196</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>34.9</v>
       </c>
       <c r="C38" t="n">
-        <v>34.95301991141709</v>
+        <v>34.96573846829587</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05301991141708839</v>
+        <v>0.06573846829586927</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0028111110066759</v>
+        <v>0.004321546213887009</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>35.3</v>
       </c>
       <c r="C39" t="n">
-        <v>34.72306620000119</v>
+        <v>34.63468672597894</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5769337999988053</v>
+        <v>-0.6653132740210594</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3328526095810615</v>
+        <v>0.4426417525886213</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>35.7</v>
       </c>
       <c r="C40" t="n">
-        <v>35.16858681465516</v>
+        <v>35.09637430240712</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5314131853448387</v>
+        <v>-0.6036256975928822</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2823999735583479</v>
+        <v>0.3643639827944937</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>36.3</v>
       </c>
       <c r="C41" t="n">
-        <v>35.61014068077346</v>
+        <v>35.99824898404957</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6898593192265352</v>
+        <v>-0.3017510159504297</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4759058803236986</v>
+        <v>0.09105367562711651</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>36.8</v>
       </c>
       <c r="C42" t="n">
-        <v>35.68210540268343</v>
+        <v>36.3463700262365</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.117894597316571</v>
+        <v>-0.4536299737634977</v>
       </c>
       <c r="E42" t="n">
-        <v>1.249688330709579</v>
+        <v>0.2057801530966716</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>37.3</v>
       </c>
       <c r="C43" t="n">
-        <v>36.89876293834338</v>
+        <v>37.34454902336046</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4012370616566159</v>
+        <v>0.04454902336046729</v>
       </c>
       <c r="E43" t="n">
-        <v>0.160991179646835</v>
+        <v>0.00198461548237146</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>37.9</v>
       </c>
       <c r="C44" t="n">
-        <v>37.87543651653033</v>
+        <v>37.87442187894351</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.02456348346967019</v>
+        <v>-0.02557812105649049</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0006033647201647606</v>
+        <v>0.000654240276780482</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>38.5</v>
       </c>
       <c r="C45" t="n">
-        <v>38.58766495887683</v>
+        <v>38.24018622697763</v>
       </c>
       <c r="D45" t="n">
-        <v>0.08766495887682879</v>
+        <v>-0.2598137730223726</v>
       </c>
       <c r="E45" t="n">
-        <v>0.007685145014876083</v>
+        <v>0.06750319665212097</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>38.9</v>
       </c>
       <c r="C46" t="n">
-        <v>39.10540492532465</v>
+        <v>38.79043648578719</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2054049253246504</v>
+        <v>-0.1095635142128089</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0421911833476252</v>
+        <v>0.01200416364666037</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>39.4</v>
       </c>
       <c r="C47" t="n">
-        <v>40.05100399181302</v>
+        <v>39.2829732093281</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6510039918130204</v>
+        <v>-0.1170267906719005</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4238061973564871</v>
+        <v>0.01369526973496481</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>39.9</v>
       </c>
       <c r="C48" t="n">
-        <v>40.56251715606416</v>
+        <v>39.74194275022238</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6625171560641618</v>
+        <v>-0.1580572497776203</v>
       </c>
       <c r="E48" t="n">
-        <v>0.438928982079345</v>
+        <v>0.02498209420726504</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>40.1</v>
       </c>
       <c r="C49" t="n">
-        <v>38.33997861283432</v>
+        <v>39.64644768791061</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.760021387165686</v>
+        <v>-0.4535523120893927</v>
       </c>
       <c r="E49" t="n">
-        <v>3.097675283280626</v>
+        <v>0.2057096998016339</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>40.6</v>
       </c>
       <c r="C50" t="n">
-        <v>40.43296999164407</v>
+        <v>40.35913214491011</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1670300083559297</v>
+        <v>-0.2408678550898955</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02789902369138196</v>
+        <v>0.05801732361560689</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>40.9</v>
       </c>
       <c r="C51" t="n">
-        <v>40.02033061713695</v>
+        <v>40.86678455558218</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.8796693828630495</v>
+        <v>-0.03321544441782009</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7738182231466584</v>
+        <v>0.001103265747873296</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-3.821628583580964</v>
+        <v>-7.135290402038716</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>15.25440955466331</v>
+        <v>3.868404387449068</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.3050881910932662</v>
+        <v>0.07736808774898137</v>
       </c>
     </row>
   </sheetData>
